--- a/backend/imagenes/Merida Yucatan/1/Formato Mérida.xlsx
+++ b/backend/imagenes/Merida Yucatan/1/Formato Mérida.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="59">
   <si>
     <t>Ciudad</t>
   </si>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>100m²</t>
+  </si>
+  <si>
+    <t>Negociable</t>
   </si>
   <si>
     <t>Privada Kutz, 97308 Yucatán Country Club, Yuc.</t>
@@ -950,7 +953,7 @@
         <v>15</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -958,7 +961,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" s="3">
         <v>50000.0</v>
@@ -976,16 +979,16 @@
         <v>6.0</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -993,7 +996,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16" s="3">
         <v>80000.0</v>
@@ -1011,10 +1014,10 @@
         <v>15.0</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>15</v>
@@ -1028,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C17" s="3">
         <v>38000.0</v>
@@ -1046,40 +1049,32 @@
         <v>6.0</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="A18" s="2"/>
       <c r="B18" s="5"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="A19" s="2"/>
       <c r="B19" s="5"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="A20" s="2"/>
       <c r="B20" s="5"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="A21" s="2"/>
       <c r="B21" s="5"/>
     </row>
   </sheetData>
